--- a/docs/modele-import-ceil.xlsx
+++ b/docs/modele-import-ceil.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:K4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -418,12 +418,21 @@
         <v>Prénom arabe</v>
       </c>
       <c r="F1" t="str">
+        <v>Date de naissance</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Lieu de naissance</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Lieu de naissance arabe</v>
+      </c>
+      <c r="I1" t="str">
         <v>Type</v>
       </c>
-      <c r="G1" t="str">
+      <c r="J1" t="str">
         <v>Téléphone</v>
       </c>
-      <c r="H1" t="str">
+      <c r="K1" t="str">
         <v>Email</v>
       </c>
     </row>
@@ -444,12 +453,21 @@
         <v>أمينة</v>
       </c>
       <c r="F2" t="str">
+        <v>28/07/1998</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Mostaganem</v>
+      </c>
+      <c r="H2" t="str">
+        <v>مستغانم</v>
+      </c>
+      <c r="I2" t="str">
         <v>Étudiant</v>
       </c>
-      <c r="G2" t="str">
+      <c r="J2" t="str">
         <v>0550112233</v>
       </c>
-      <c r="H2" t="str">
+      <c r="K2" t="str">
         <v>amina.benali@example.dz</v>
       </c>
     </row>
@@ -470,12 +488,21 @@
         <v/>
       </c>
       <c r="F3" t="str">
+        <v>vers 1975</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Oran</v>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
         <v>Enseignant</v>
       </c>
-      <c r="G3" t="str">
+      <c r="J3" t="str">
         <v>0661445566</v>
       </c>
-      <c r="H3" t="str">
+      <c r="K3" t="str">
         <v/>
       </c>
     </row>
@@ -504,10 +531,19 @@
       <c r="H4" t="str">
         <v/>
       </c>
+      <c r="I4" t="str">
+        <v/>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K4"/>
   </ignoredErrors>
 </worksheet>
 </file>
